--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.03263511765743</v>
+        <v>6.830303206619332</v>
       </c>
       <c r="D2" t="n">
-        <v>41.96780213644996</v>
+        <v>6.819767847173119</v>
       </c>
       <c r="E2" t="n">
-        <v>5.381272639069163</v>
+        <v>0.8744568038487391</v>
       </c>
       <c r="F2" t="n">
-        <v>5.301173834806103</v>
+        <v>0.8614407481559916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.40714542419686</v>
+        <v>4.778661131431989</v>
       </c>
       <c r="D3" t="n">
-        <v>29.52366605188466</v>
+        <v>4.797595733431257</v>
       </c>
       <c r="E3" t="n">
-        <v>5.381272639069163</v>
+        <v>0.8744568038487391</v>
       </c>
       <c r="F3" t="n">
-        <v>5.301173834806103</v>
+        <v>0.8614407481559916</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7529724973407</v>
+        <v>6.947358030817864</v>
       </c>
       <c r="D4" t="n">
-        <v>42.61616281452504</v>
+        <v>6.925126457360319</v>
       </c>
       <c r="E4" t="n">
-        <v>5.381272639069163</v>
+        <v>0.8744568038487391</v>
       </c>
       <c r="F4" t="n">
-        <v>5.301173834806103</v>
+        <v>0.8614407481559916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.01332532662478</v>
+        <v>5.852165365576527</v>
       </c>
       <c r="D5" t="n">
-        <v>35.87162579534566</v>
+        <v>5.82913919174367</v>
       </c>
       <c r="E5" t="n">
-        <v>5.381272639069163</v>
+        <v>0.8744568038487391</v>
       </c>
       <c r="F5" t="n">
-        <v>5.301173834806103</v>
+        <v>0.8614407481559916</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
